--- a/플랜트구매품질팀_대시보드_Template.xlsx
+++ b/플랜트구매품질팀_대시보드_Template.xlsx
@@ -1581,5 +1581,7 @@
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{0735ee20-8799-47cb-9476-621096ec91fa}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/플랜트구매품질팀_대시보드_Template.xlsx
+++ b/플랜트구매품질팀_대시보드_Template.xlsx
@@ -5,7 +5,7 @@
     <sheet name="📖 README" sheetId="1" r:id="rId1"/>
     <sheet name="프로젝트_현황" sheetId="2" r:id="rId2"/>
     <sheet name="프로젝트_구매품질 실적" sheetId="3" r:id="rId3"/>
-    <sheet name="프로젝트_미결 NCR 현황" sheetId="4" r:id="rId4"/>
+    <sheet name="프로젝트_NCR처리현황" sheetId="4" r:id="rId4"/>
     <sheet name="PQAN" sheetId="5" r:id="rId5"/>
     <sheet name="TPA_목록" sheetId="6" r:id="rId6"/>
     <sheet name="TPA_집행현황" sheetId="7" r:id="rId7"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t xml:space="preserve">플랜트구매품질팀 통합관리 대시보드 - Excel 입력 양식</t>
   </si>
@@ -27,7 +27,7 @@
     <t xml:space="preserve">사용 방법</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 아래 시트탭의 각 시트(프로젝트_현황 / 프로젝트_구매품질 실적 / 프로젝트_미결 NCR 현황 / PQAN / TPA_목록 / TPA_집행현황 / TPA_월별대금청구현황 / 인력운영_현황 / 인력운영_세부내역 / 출장현황 / 주요현안)에 데이터를 입력합니다.</t>
+    <t xml:space="preserve">1. 아래 시트탭의 각 시트(프로젝트_현황 / 프로젝트_구매품질 실적 / 프로젝트_NCR처리현황 / PQAN / TPA_목록 / TPA_집행현황 / TPA_월별대금청구현황 / 인력운영_현황 / 인력운영_세부내역 / 출장현황 / 주요현안)에 데이터를 입력합니다.</t>
   </si>
   <si>
     <t xml:space="preserve">2. 1행의 컬럼명(헤더)은 절대 변경하지 마세요. 시트명도 그대로 유지해야 합니다.</t>
@@ -60,12 +60,15 @@
     <t xml:space="preserve">• 프로젝트_현황 시트의 계약가는 백만 단위 (USD M / KRW M)로 입력합니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">• 날짜 필드(Issue_Date, 출발일, 복귀일, PQAN 배포일자, 업무 종료 예상 시기)는 Excel 날짜 형식으로 입력해주세요.</t>
+    <t xml:space="preserve">• 날짜 필드(Issue Date / Due Date / Closed Date, 출발일, 복귀일, PQAN 배포일자 등)는 Excel 날짜 형식 또는 YYYY-MM-DD로 입력해주세요.</t>
   </si>
   <si>
     <t xml:space="preserve">신규 시트 입력 가이드</t>
   </si>
   <si>
+    <t xml:space="preserve">• 프로젝트_NCR처리현황 시트: Main Vendor / Sub Vendor / 공종 / Issued by 포함 flat 컬럼. 작업공종·근본원인·처리분류는 대·중·(소)분류 분리 입력 후 HPMS 계층으로 자동 변환됩니다. Action Status 컬럼은 대시보드 확장 행에서 직접 입력 후 Excel 재다운로드 시 자동 저장됩니다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">• PQAN 시트: 동일 PQAN No. 중복 입력 허용 (이미지/내용을 여러 행으로 분리). 대시보드는 자동으로 통합 표시합니다.</t>
   </si>
   <si>
@@ -96,10 +99,10 @@
     <t xml:space="preserve">• 예산 대비 집행 70% 초과 → '1차 청산추정 필요'</t>
   </si>
   <si>
-    <t xml:space="preserve">• 예산 대비 집행 90% 초과 → '2차 청산추정 및 예산외품의 준비 필요'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• 계약고 대비 집행 90% 초과 → '계약고 증액 절차 필요'</t>
+    <t xml:space="preserve">• 예산 대비 집행 90% 초과 → '2차 청산추정 및 예산외품의 검토 필요'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 계약고 대비 집행 90% 초과 → '계약고 증액 필요'</t>
   </si>
   <si>
     <t xml:space="preserve">단계별 가중치 (참고)</t>
@@ -132,7 +135,7 @@
     <t xml:space="preserve">국가</t>
   </si>
   <si>
-    <t xml:space="preserve">PM</t>
+    <t xml:space="preserve">PD</t>
   </si>
   <si>
     <t xml:space="preserve">PQCM</t>
@@ -183,208 +186,229 @@
     <t xml:space="preserve">NCR_Done</t>
   </si>
   <si>
-    <t xml:space="preserve">Serial_Number</t>
+    <t xml:space="preserve">NCR No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">품목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issued by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Issue Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업공종 대공종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업공종 중공종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작업공종 소공종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근본원인 대분류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근본원인 중분류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">처리분류 대분류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">처리분류 중분류</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCR Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">순번</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PQAN No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PQAN 배포일자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">작성자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">검토자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmittal No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공급업체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지역</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발견 시기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">발견 장소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">개요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">원인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">후속/예방 조치 (권고)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이미지 URL (Teams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등록평가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정기평가 (2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정기평가 (2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPA 예산 (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPA 계약고 (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">집행비용 (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPA 예산 (KRW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPA 계약고 (KRW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">집행비용 (KRW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예산 소진율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現 계약고 소진율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">청구연월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지급대금</t>
+  </si>
+  <si>
+    <t xml:space="preserve">단위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">소속</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근무지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">직급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당 공종</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PQC_Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number_of_PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">업무 종료 예상 시기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRC %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당자(정)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">담당자(부)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출장자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출장목적</t>
+  </si>
+  <si>
+    <t xml:space="preserve">방문업체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">출발일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">복귀일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
   </si>
   <si>
     <t xml:space="preserve">Project_Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR_Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR_Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Issue_Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days_to_Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">순번</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PQAN No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PQAN 배포일자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">연</t>
-  </si>
-  <si>
-    <t xml:space="preserve">월</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feedback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">작성자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">검토자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공종</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCR No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmittal No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">품목</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공급업체</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지역</t>
-  </si>
-  <si>
-    <t xml:space="preserve">발견 시기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">발견 장소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">개요</t>
-  </si>
-  <si>
-    <t xml:space="preserve">원인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">후속/예방 조치 (권고)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이미지 URL (Teams)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">등록평가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정기평가 (2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정기평가 (2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPA 예산 (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPA 계약고 (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">집행비용 (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPA 예산 (KRW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPA 계약고 (KRW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">집행비용 (KRW)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예산 소진율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現 계약고 소진율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">청구연월</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지급대금</t>
-  </si>
-  <si>
-    <t xml:space="preserve">단위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이름</t>
-  </si>
-  <si>
-    <t xml:space="preserve">소속</t>
-  </si>
-  <si>
-    <t xml:space="preserve">근무지</t>
-  </si>
-  <si>
-    <t xml:space="preserve">직급</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">담당 공종</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PQC_Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number_of_PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">업무 종료 예상 시기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRC %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">담당자(정)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">담당자(부)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출장자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출장목적</t>
-  </si>
-  <si>
-    <t xml:space="preserve">방문업체</t>
-  </si>
-  <si>
-    <t xml:space="preserve">출발일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">복귀일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner</t>
   </si>
   <si>
     <t xml:space="preserve">Action_Required</t>
@@ -580,14 +604,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" t="s" s="2">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" t="s" s="0">
         <v>23</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" t="s" s="0">
+    <row r="28"/>
+    <row r="29" ht="17.25" customHeight="1">
+      <c r="A29" t="s" s="2">
         <v>24</v>
       </c>
     </row>
@@ -601,20 +625,25 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33" ht="17.25" customHeight="1">
-      <c r="A33" t="s" s="2">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" t="s" s="0">
         <v>27</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" t="s" s="0">
+    <row r="33"/>
+    <row r="34" ht="17.25" customHeight="1">
+      <c r="A34" t="s" s="2">
         <v>28</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" t="s" s="0">
         <v>29</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" t="s" s="0">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -636,37 +665,37 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -689,28 +718,28 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -727,16 +756,16 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -758,40 +787,40 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L1" t="s" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -807,43 +836,43 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L1" t="s" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M1" t="s" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -856,12 +885,29 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="36" customWidth="1"/>
+    <col min="20" max="20" width="36" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="3">
         <v>55</v>
@@ -886,6 +932,39 @@
       </c>
       <c r="I1" t="s" s="3">
         <v>62</v>
+      </c>
+      <c r="J1" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K1" t="s" s="3">
+        <v>64</v>
+      </c>
+      <c r="L1" t="s" s="3">
+        <v>65</v>
+      </c>
+      <c r="M1" t="s" s="3">
+        <v>66</v>
+      </c>
+      <c r="N1" t="s" s="3">
+        <v>67</v>
+      </c>
+      <c r="O1" t="s" s="3">
+        <v>68</v>
+      </c>
+      <c r="P1" t="s" s="3">
+        <v>69</v>
+      </c>
+      <c r="Q1" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="R1" t="s" s="3">
+        <v>71</v>
+      </c>
+      <c r="S1" t="s" s="3">
+        <v>72</v>
+      </c>
+      <c r="T1" t="s" s="3">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -912,76 +991,76 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" t="s" s="3">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="L1" t="s" s="3">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="M1" t="s" s="3">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="N1" t="s" s="3">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O1" t="s" s="3">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="P1" t="s" s="3">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q1" t="s" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R1" t="s" s="3">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="S1" t="s" s="3">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="T1" t="s" s="3">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="U1" t="s" s="3">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="V1" t="s" s="3">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="W1" t="s" s="3">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X1" t="s" s="3">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1001,19 +1080,19 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1030,34 +1109,34 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1078,22 +1157,22 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1118,42 +1197,36 @@
   <sheetData>
     <row r="1" ht="26.1" customHeight="1">
       <c r="A1" t="s" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s" s="3">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C1" t="s" s="3">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D1" t="s" s="3">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E1" t="s" s="3">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I1" t="s" s="3">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="J1" t="s" s="3">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{f6a4f584-0b4b-4f3e-9ee5-30473aa69edf}" removed="1"/>
-</clbl:labelList>
 </file>
--- a/플랜트구매품질팀_대시보드_Template.xlsx
+++ b/플랜트구매품질팀_대시보드_Template.xlsx
@@ -1229,4 +1229,10 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" enabled="0" method="" siteId="{5fcb0def-a698-40ce-a73a-ea61130c13c6}" actionId="{9f2d86d3-46d4-4eaf-841d-c6c259eb65ff}" removed="1"/>
+</clbl:labelList>
 </file>